--- a/backend/output_maquettes/MAQUETTE_A_AFFECTATION_GI.xlsx
+++ b/backend/output_maquettes/MAQUETTE_A_AFFECTATION_GI.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>GI S2</t>
+          <t>GP-GI S2</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
